--- a/restaurant_evaluation_forms/024_monthly_restaurant_employee_evaluation_form--restaurant_evaluation_forms.xlsx
+++ b/restaurant_evaluation_forms/024_monthly_restaurant_employee_evaluation_form--restaurant_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'front_of_house'}</t>
+          <t>front_of_house</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Front of House'}</t>
+          <t>Front of House</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'back_of_house'}</t>
+          <t>back_of_house</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Back of House'}</t>
+          <t>Back of House</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'outstanding'}</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Outstanding'}</t>
+          <t>Outstanding</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Needs Improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
